--- a/tools/importer/reports/import-acs-assessment.report.xlsx
+++ b/tools/importer/reports/import-acs-assessment.report.xlsx
@@ -106,7 +106,7 @@
     <t>acs-assessment</t>
   </si>
   <si>
-    <t>2026-10-13T16:27:01.447Z</t>
+    <t>2026-10-13T16:50:25.165Z</t>
   </si>
   <si>
     <t>Assess and Plan Your Analytics Modernization Path</t>
